--- a/data/trans_orig/IP2003-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2003-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>13828</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27046</t>
+          <t>25840</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18928</t>
+          <t>19390</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25307</t>
+          <t>25858</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41748</t>
+          <t>42051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61168</t>
+          <t>62374</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74118</t>
+          <t>74386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63764</t>
+          <t>63302</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74616</t>
+          <t>74519</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129157</t>
+          <t>128854</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145598</t>
+          <t>145047</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65017</t>
+          <t>65121</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89814</t>
+          <t>91451</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53106</t>
+          <t>54205</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77757</t>
+          <t>78132</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>124981</t>
+          <t>125336</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159059</t>
+          <t>159683</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>304502</t>
+          <t>302865</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>329299</t>
+          <t>329195</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>377011</t>
+          <t>376636</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>401662</t>
+          <t>400563</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>690025</t>
+          <t>689401</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>724103</t>
+          <t>723748</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,24%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23257</t>
+          <t>23530</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>13446</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27025</t>
+          <t>27201</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27678</t>
+          <t>27978</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45885</t>
+          <t>46064</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>139254</t>
+          <t>138981</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>151835</t>
+          <t>151536</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119678</t>
+          <t>119502</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132860</t>
+          <t>133257</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>263329</t>
+          <t>263150</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>281536</t>
+          <t>281236</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98898</t>
+          <t>98461</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129850</t>
+          <t>130729</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83435</t>
+          <t>84137</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111397</t>
+          <t>111514</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190813</t>
+          <t>190408</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>234248</t>
+          <t>233928</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>515190</t>
+          <t>514311</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>546142</t>
+          <t>546579</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>572766</t>
+          <t>572649</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>600728</t>
+          <t>600026</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1094955</t>
+          <t>1095275</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1138390</t>
+          <t>1138795</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,68%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25350</t>
+          <t>24694</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10266</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22760</t>
+          <t>22716</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26552</t>
+          <t>26650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44478</t>
+          <t>43726</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>64065</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76047</t>
+          <t>75729</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59865</t>
+          <t>59909</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72359</t>
+          <t>72164</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126906</t>
+          <t>127658</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144832</t>
+          <t>144734</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58295</t>
+          <t>56828</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83536</t>
+          <t>83310</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53633</t>
+          <t>53140</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76893</t>
+          <t>78417</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117575</t>
+          <t>117916</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153266</t>
+          <t>153460</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>335504</t>
+          <t>335730</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>360745</t>
+          <t>362212</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>387258</t>
+          <t>385734</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>410518</t>
+          <t>411011</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>729924</t>
+          <t>729730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>765615</t>
+          <t>765274</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16370</t>
+          <t>16702</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31202</t>
+          <t>31855</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>17316</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26180</t>
+          <t>26209</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45841</t>
+          <t>44140</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123891</t>
+          <t>123238</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138723</t>
+          <t>138391</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137692</t>
+          <t>138706</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148746</t>
+          <t>150111</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265275</t>
+          <t>266976</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>284936</t>
+          <t>284907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96409</t>
+          <t>96632</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127193</t>
+          <t>128679</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79337</t>
+          <t>79058</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107849</t>
+          <t>108814</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>182110</t>
+          <t>183597</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>225735</t>
+          <t>225260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>535698</t>
+          <t>534212</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>566482</t>
+          <t>566259</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>594950</t>
+          <t>593985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>623462</t>
+          <t>623741</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1139955</t>
+          <t>1140430</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1183580</t>
+          <t>1182093</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,56%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>18309</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>11871</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>25238</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46707</t>
+          <t>46772</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54078</t>
+          <t>54095</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49156</t>
+          <t>49065</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59664</t>
+          <t>59812</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98826</t>
+          <t>98400</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111766</t>
+          <t>111767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54715</t>
+          <t>54300</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78513</t>
+          <t>79457</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48918</t>
+          <t>48727</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73754</t>
+          <t>71610</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108915</t>
+          <t>108563</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143334</t>
+          <t>142270</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>361852</t>
+          <t>360908</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>385650</t>
+          <t>386065</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>390029</t>
+          <t>392173</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>414865</t>
+          <t>415056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>760814</t>
+          <t>761878</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>795233</t>
+          <t>795585</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,99%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>11831</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26417</t>
+          <t>24798</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12521</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26386</t>
+          <t>26085</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27555</t>
+          <t>27742</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46859</t>
+          <t>47996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135508</t>
+          <t>137127</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149795</t>
+          <t>150094</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143352</t>
+          <t>143653</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157217</t>
+          <t>156967</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284804</t>
+          <t>283667</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>304108</t>
+          <t>303921</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,64%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74365</t>
+          <t>73987</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103934</t>
+          <t>105283</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78067</t>
+          <t>77560</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107974</t>
+          <t>108202</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160639</t>
+          <t>158663</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>202155</t>
+          <t>200926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>554621</t>
+          <t>553272</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>584190</t>
+          <t>584568</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>592921</t>
+          <t>592693</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>622828</t>
+          <t>623335</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1157294</t>
+          <t>1158523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1198810</t>
+          <t>1200786</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17986</t>
+          <t>17396</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1434</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21570</t>
+          <t>23803</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35713</t>
+          <t>36303</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50755</t>
+          <t>50867</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49599</t>
+          <t>49783</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58369</t>
+          <t>58010</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>91932</t>
+          <t>89699</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107811</t>
+          <t>107086</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56195</t>
+          <t>56008</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>149613</t>
+          <t>159620</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60373</t>
+          <t>59918</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113388</t>
+          <t>119009</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127137</t>
+          <t>128339</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236169</t>
+          <t>246090</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>303804</t>
+          <t>293797</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>397222</t>
+          <t>397409</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>392195</t>
+          <t>386574</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>445210</t>
+          <t>445665</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>722832</t>
+          <t>712911</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>831864</t>
+          <t>830662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,62%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15161</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29723</t>
+          <t>29529</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14754</t>
+          <t>14806</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31746</t>
+          <t>32288</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34270</t>
+          <t>32627</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55487</t>
+          <t>54954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117815</t>
+          <t>118009</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>132377</t>
+          <t>132312</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150333</t>
+          <t>149791</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>167325</t>
+          <t>167273</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>274130</t>
+          <t>274663</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>295347</t>
+          <t>296990</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83542</t>
+          <t>84360</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>192835</t>
+          <t>190087</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85121</t>
+          <t>84499</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>138824</t>
+          <t>142608</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>180762</t>
+          <t>179041</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>298966</t>
+          <t>304557</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>461819</t>
+          <t>464567</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>571112</t>
+          <t>570294</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>608641</t>
+          <t>604857</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>662344</t>
+          <t>662966</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1103153</t>
+          <t>1097562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1221357</t>
+          <t>1223078</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2003-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2003-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12989</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8156</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18839</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15,71%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>22,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>19822</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13828</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>25840</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14146</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>26623</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>22,47%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12989</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8173</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19390</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>15,71%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25858</t>
+          <t>24899</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42051</t>
+          <t>41773</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>69703</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>63853</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>74536</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>84,29%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>90,14%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>68392</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>62374</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>74386</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>61591</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>74068</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>77,53%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>70,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,32%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>69703</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>63302</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>74519</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>84,29%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128854</t>
+          <t>129132</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145047</t>
+          <t>146006</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,43%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82692</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82692</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82692</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88214</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88214</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88214</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82692</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82692</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82692</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>65224</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>53786</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>77963</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,34%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,83%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,14%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>76934</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>65121</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>91451</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>65157</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>90314</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>19,51%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,19%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>65224</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>54205</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>78132</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,34%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>125336</t>
+          <t>126166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159683</t>
+          <t>159564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>389544</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>376805</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>400982</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,66%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,86%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,17%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>479</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>317382</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>302865</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>329195</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>304002</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>329159</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>80,49%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>389544</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>376636</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>400563</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,66%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>689401</t>
+          <t>689520</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>723748</t>
+          <t>722918</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,14%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>454768</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>454768</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>454768</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>594</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>394316</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>394316</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>394316</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>454768</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>454768</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>454768</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19322</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13266</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>26853</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,17%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,04%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>16549</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10975</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23530</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11095</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>24079</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,18%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>19322</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>13446</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>27201</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27978</t>
+          <t>27686</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46064</t>
+          <t>45944</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>127381</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>119850</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>133437</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,83%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>81,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>90,96%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>145962</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>138981</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>151536</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>138432</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>151416</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>89,82%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>85,52%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,25%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>127381</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>119502</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>133257</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>86,83%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>263150</t>
+          <t>263270</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>281236</t>
+          <t>281528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>146703</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>146703</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>146703</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>162511</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>162511</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>162511</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>146703</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>146703</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>146703</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>97535</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>83791</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>111239</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,26%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,26%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>113305</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>98461</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>130729</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>97996</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>128552</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,57%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,26%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,27%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>97535</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>84137</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>111514</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,26%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190408</t>
+          <t>190612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>233928</t>
+          <t>233777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>586628</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>572924</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>600372</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,74%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87,75%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>794</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>531735</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>514311</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>546579</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>516488</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>547044</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>82,43%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,73%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>84,74%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>884</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>586628</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>572649</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>600026</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>85,74%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1095275</t>
+          <t>1095426</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1138795</t>
+          <t>1138591</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>684163</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>684163</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>684163</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>963</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>645040</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>645040</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>645040</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>684163</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>684163</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>684163</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15950</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10859</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22478</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19,3%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13,14%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>27,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>18215</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13030</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24694</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>12150</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>25126</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>20,52%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>15950</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10461</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>22716</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>19,3%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26650</t>
+          <t>26100</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43726</t>
+          <t>44036</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66675</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>60147</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>71766</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>80,7%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>72,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>86,86%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>70544</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>64065</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>75729</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>63633</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>76609</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>79,48%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>72,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>85,32%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>66675</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>59909</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>72164</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>80,7%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127658</t>
+          <t>127348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144734</t>
+          <t>145284</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,77%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88759</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88759</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88759</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>65513</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>53783</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>79178</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,11%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,06%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>69814</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>56828</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>83310</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>58101</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>82885</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>16,66%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13,56%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>65513</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>53140</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>78417</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117916</t>
+          <t>117181</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153460</t>
+          <t>154697</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>398638</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>384973</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>410368</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,89%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,94%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>506</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>349226</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>335730</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>362212</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>336155</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>360939</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>83,34%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>80,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,44%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>398638</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>385734</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>411011</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,89%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>729730</t>
+          <t>728493</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>765274</t>
+          <t>766009</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>464151</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>464151</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>464151</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>606</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>419040</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>419040</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>419040</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>464151</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>464151</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>464151</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,107 +3012,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11333</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17852</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,44%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>23202</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16702</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31855</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>15987</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>31215</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>14,96%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11333</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5911</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17316</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>20,13%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>34535</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>25976</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>45288</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>11,1%</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>34535</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>26209</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>44140</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -3125,107 +3125,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>144689</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>138170</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>149312</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,56%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,7%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>131891</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>123238</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>138391</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>123878</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>139106</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>85,04%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>79,46%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>144689</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>138706</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>150111</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,74%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>79,87%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>89,69%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>276581</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>265828</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>285140</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>88,9%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>96,21%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>276581</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>266976</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>284907</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>88,9%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>156022</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>156022</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>156022</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155093</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155093</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155093</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>156022</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>156022</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>156022</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>92797</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>80047</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>108689</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>111231</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>96632</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>128679</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>95300</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>127320</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>16,78%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,41%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>92797</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>79058</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>108814</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>183597</t>
+          <t>180949</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>225260</t>
+          <t>224368</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>610002</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>594110</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>622752</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,8%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,61%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>796</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>551660</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>534212</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>566259</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>535571</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>567591</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>83,22%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80,59%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>85,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>610002</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>593985</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>623741</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>86,8%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1140430</t>
+          <t>1141322</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1182093</t>
+          <t>1184741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,75%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>702799</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>702799</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>702799</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>954</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>662891</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>662891</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>662891</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>702799</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>702799</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>702799</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12553</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7736</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18515</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>18,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,48%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>27,48%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5055</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2170</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9493</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10476</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,98%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12553</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7562</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18309</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>18,63%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11871</t>
+          <t>11981</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>24686</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>54821</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48859</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>59638</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>81,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>72,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,52%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>51210</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>46772</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54095</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>45789</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>53962</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,02%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>83,13%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,14%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>54821</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>49065</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>59812</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>81,37%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98400</t>
+          <t>98952</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111767</t>
+          <t>111657</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>67374</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>67374</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>67374</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56265</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>56265</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>56265</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>67374</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>67374</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>67374</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>59595</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>47583</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>72241</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,26%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>15,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>66095</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54300</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>79457</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>53092</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>79188</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>15,01%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12,33%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,04%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>59595</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>48727</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>71610</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,85%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108563</t>
+          <t>109427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142270</t>
+          <t>144312</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>404188</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>391542</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>416200</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>84,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>89,74%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>566</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>374270</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>360908</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>386065</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>361177</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>387273</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>84,99%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81,96%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>87,67%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>404188</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>392173</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>415056</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>87,15%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>761878</t>
+          <t>759836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>795585</t>
+          <t>794721</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,9%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>463783</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>463783</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>463783</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>662</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>440365</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>440365</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>440365</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>463783</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>463783</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>463783</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18753</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13172</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>27041</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,05%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,93%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>17805</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11831</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24798</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11852</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>25258</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>18753</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>12771</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>26085</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,05%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27742</t>
+          <t>27453</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47996</t>
+          <t>47428</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>150985</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>142697</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>156566</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,95%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,07%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,24%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>144120</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>137127</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>150094</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>136667</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>150073</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>89,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,69%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,69%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>150985</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>143653</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>156967</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,95%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>283667</t>
+          <t>284235</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>303921</t>
+          <t>304210</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>169738</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>169738</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>169738</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>161925</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>161925</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>161925</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>169738</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>169738</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>169738</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>90901</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>77447</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>106142</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,97%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,05%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,14%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>88955</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>73987</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>105283</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>73998</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>103586</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,51%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,23%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,99%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>90901</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>77560</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>108202</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>158663</t>
+          <t>159691</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>200926</t>
+          <t>201619</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>609994</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>594753</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>623448</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,03%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,86%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,95%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>860</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>569600</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>553272</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>584568</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>554969</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>584557</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>86,49%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,01%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>874</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>609994</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>592693</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>623335</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1158523</t>
+          <t>1157830</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1200786</t>
+          <t>1199758</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,25%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>988</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>658555</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>658555</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>658555</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3644</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8511</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7435</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17396</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23803</t>
+          <t>14160</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>51289</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46422</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>53690</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>84,51%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,74%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>46264</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>36303</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>50867</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>86,15%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>67,6%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55343</t>
+          <t>41265</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49783</t>
+          <t>36921</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58010</t>
+          <t>43953</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>101607</t>
+          <t>92555</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89699</t>
+          <t>86678</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107086</t>
+          <t>96279</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>113502</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>113502</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113502</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>71619</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56278</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>100126</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,34%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,05%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,45%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>83817</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>56008</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>159620</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>18,49%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12,35%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>78881</t>
+          <t>60796</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59918</t>
+          <t>48466</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>119009</t>
+          <t>76089</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>162698</t>
+          <t>132415</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>128339</t>
+          <t>114037</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>246090</t>
+          <t>165220</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>395241</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>366734</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>410582</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,66%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,55%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,95%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>546</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>369600</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>293797</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>397409</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>81,51%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>64,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>87,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>426702</t>
+          <t>365317</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>386574</t>
+          <t>350024</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>445665</t>
+          <t>377647</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>796303</t>
+          <t>760558</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>712911</t>
+          <t>727753</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>830662</t>
+          <t>778936</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466860</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466860</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466860</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>453417</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>453417</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>453417</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505583</t>
+          <t>426113</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505583</t>
+          <t>426113</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505583</t>
+          <t>426113</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>959001</t>
+          <t>892973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>959001</t>
+          <t>892973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>959001</t>
+          <t>892973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19647</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12521</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28835</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,48%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,23%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>21796</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15226</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29529</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>22145</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14806</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32288</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>43818</t>
+          <t>41792</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32627</t>
+          <t>31837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54954</t>
+          <t>53587</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>147749</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>138561</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>154875</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,77%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>125742</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>118009</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>132312</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>85,23%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>79,99%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>160057</t>
+          <t>126155</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149791</t>
+          <t>118768</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>167273</t>
+          <t>133420</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>285799</t>
+          <t>273904</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>274663</t>
+          <t>262109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>296990</t>
+          <t>283859</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167396</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167396</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167396</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>147538</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>147538</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>147538</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>148300</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>148300</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>148300</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>315696</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>315696</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>315696</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>94910</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>77347</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>124939</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,13%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>113048</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>84360</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>190087</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>17,27%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>105364</t>
+          <t>87580</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84499</t>
+          <t>73382</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142608</t>
+          <t>104258</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>218412</t>
+          <t>182490</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>179041</t>
+          <t>159697</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>304557</t>
+          <t>214093</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>594280</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>564251</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>611843</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,87%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>800</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>541606</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>464567</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>570294</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>82,73%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>70,96%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,11%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>837</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>642101</t>
+          <t>532737</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>604857</t>
+          <t>516059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>662966</t>
+          <t>546935</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1183707</t>
+          <t>1127017</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1097562</t>
+          <t>1095414</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1223078</t>
+          <t>1149810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,8%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>920</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>654654</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>654654</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>654654</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620317</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620317</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620317</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1402119</t>
+          <t>1309507</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1402119</t>
+          <t>1309507</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1402119</t>
+          <t>1309507</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
